--- a/CastleHero_Table/Stage_Table.xlsx
+++ b/CastleHero_Table/Stage_Table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\CH_Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{589B3B44-42F6-4E0B-98C1-011DF11D8FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF4660C-467A-47CC-B15F-66CA86A7B4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43480" yWindow="730" windowWidth="30670" windowHeight="19010" xr2:uid="{D7A366D4-3233-4149-9445-520E7C66975E}"/>
+    <workbookView xWindow="7390" yWindow="1620" windowWidth="30700" windowHeight="19010" xr2:uid="{D7A366D4-3233-4149-9445-520E7C66975E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,101 +36,53 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Stage_index</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>스테이지 번호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Stage_Act</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>필요 행동력</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Stage_Time</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>스테이지 플레이 시간</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Stage_Rwd_First</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>최초 클리어 보상 타입</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Stage_Rwd_First_Value</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>최초 클리어 보상 타입 값</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Stage_Rwd_Exp</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>캐릭터 경험치 값</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Stage_Rwd_Gold_Min</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>골드 보상 최소 값</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Stage_Rwd_Gold_Max</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>골드 보상 최대 값</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Stage_Rwd_Item_Per</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>클리어 시 아이템 획득 확률</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Stage_Rwd_Item_ID</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>아이템 ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Stage_Rwd_Item_Value</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>아이템 수량</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Stage_Mob_Wave</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터 웨이브 그룹 ID</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -185,7 +137,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -208,36 +160,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -577,184 +510,146 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B314C0A2-0926-40E5-96A6-744A30452DA4}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.08203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.9140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.4140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.4140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="4"/>
+    <col min="1" max="1" width="10.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.08203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.9140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.4140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.4140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2">
+        <v>60</v>
+      </c>
+      <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="2">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>22</v>
+      <c r="F2" s="2">
+        <v>200</v>
+      </c>
+      <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
+        <v>500</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" s="4">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
         <v>10</v>
       </c>
-      <c r="C3" s="4">
-        <v>60</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="C3" s="2">
+        <v>90</v>
+      </c>
+      <c r="D3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="4">
-        <v>10</v>
-      </c>
-      <c r="F3" s="4">
+      <c r="E3" s="2">
+        <v>100</v>
+      </c>
+      <c r="F3" s="2">
+        <v>300</v>
+      </c>
+      <c r="G3" s="2">
         <v>200</v>
       </c>
-      <c r="G3" s="4">
-        <v>100</v>
-      </c>
-      <c r="H3" s="4">
-        <v>500</v>
-      </c>
-      <c r="L3" s="4">
-        <v>1</v>
+      <c r="H3" s="2">
+        <v>600</v>
+      </c>
+      <c r="L3" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" s="4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
         <v>10</v>
       </c>
-      <c r="C4" s="4">
-        <v>90</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="C4" s="2">
+        <v>120</v>
+      </c>
+      <c r="D4" s="2">
         <v>0</v>
       </c>
-      <c r="E4" s="4">
-        <v>100</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="E4" s="2">
+        <v>500</v>
+      </c>
+      <c r="F4" s="2">
+        <v>400</v>
+      </c>
+      <c r="G4" s="2">
         <v>300</v>
       </c>
-      <c r="G4" s="4">
-        <v>200</v>
-      </c>
-      <c r="H4" s="4">
-        <v>600</v>
-      </c>
-      <c r="L4" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4">
-        <v>120</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>500</v>
-      </c>
-      <c r="F5" s="4">
-        <v>400</v>
-      </c>
-      <c r="G5" s="4">
-        <v>300</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="H4" s="2">
         <v>700</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L4" s="2">
         <v>3</v>
       </c>
     </row>
